--- a/Module-3-DataScientist and ML/results/reports/03_model_results_report.xlsx
+++ b/Module-3-DataScientist and ML/results/reports/03_model_results_report.xlsx
@@ -468,22 +468,22 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.59</v>
+        <v>0.275</v>
       </c>
       <c r="C2" t="n">
-        <v>0.5330945315811785</v>
+        <v>0.5054617969138875</v>
       </c>
       <c r="D2" t="n">
-        <v>0.59</v>
+        <v>0.275</v>
       </c>
       <c r="E2" t="n">
-        <v>0.5310549428104575</v>
+        <v>0.2646123352331708</v>
       </c>
       <c r="F2" t="n">
-        <v>0.601875</v>
+        <v>0.5422832839063206</v>
       </c>
       <c r="G2" t="n">
-        <v>0.007288689868556649</v>
+        <v>0.01121045676762574</v>
       </c>
       <c r="H2" t="inlineStr"/>
     </row>
@@ -494,22 +494,22 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.575</v>
+        <v>0.495</v>
       </c>
       <c r="C3" t="n">
-        <v>0.5481776744944553</v>
+        <v>0.5342368578255675</v>
       </c>
       <c r="D3" t="n">
-        <v>0.575</v>
+        <v>0.495</v>
       </c>
       <c r="E3" t="n">
-        <v>0.5492440182692173</v>
+        <v>0.504279783860739</v>
       </c>
       <c r="F3" t="n">
-        <v>0.5981249999999999</v>
+        <v>0.7054656512771696</v>
       </c>
       <c r="G3" t="n">
-        <v>0.02619040854969621</v>
+        <v>0.0224903962263741</v>
       </c>
       <c r="H3" t="inlineStr"/>
     </row>
@@ -520,22 +520,22 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.6274999999999999</v>
+        <v>0.62</v>
       </c>
       <c r="C4" t="n">
-        <v>0.6177623380769932</v>
+        <v>0.6138534798534798</v>
       </c>
       <c r="D4" t="n">
-        <v>0.6274999999999999</v>
+        <v>0.62</v>
       </c>
       <c r="E4" t="n">
-        <v>0.618548815304829</v>
+        <v>0.6147931884919874</v>
       </c>
       <c r="F4" t="n">
-        <v>0.64</v>
+        <v>0.7862007102844799</v>
       </c>
       <c r="G4" t="n">
-        <v>0.01634587103827755</v>
+        <v>0.05338415720984872</v>
       </c>
       <c r="H4" t="inlineStr">
         <is>
@@ -586,13 +586,13 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.7142857142857143</v>
+        <v>0.6428571428571429</v>
       </c>
       <c r="C2" t="n">
-        <v>0.5</v>
+        <v>0.45</v>
       </c>
       <c r="D2" t="n">
-        <v>0.5882352941176471</v>
+        <v>0.5294117647058824</v>
       </c>
       <c r="E2" t="n">
         <v>20</v>
@@ -605,13 +605,13 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.674074074074074</v>
+        <v>0.6692307692307692</v>
       </c>
       <c r="C3" t="n">
-        <v>0.7615062761506276</v>
+        <v>0.7280334728033473</v>
       </c>
       <c r="D3" t="n">
-        <v>0.7151277013752456</v>
+        <v>0.6973947895791583</v>
       </c>
       <c r="E3" t="n">
         <v>239</v>
@@ -624,13 +624,13 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.5086206896551724</v>
+        <v>0.5158730158730159</v>
       </c>
       <c r="C4" t="n">
-        <v>0.4184397163120567</v>
+        <v>0.4609929078014184</v>
       </c>
       <c r="D4" t="n">
-        <v>0.4591439688715953</v>
+        <v>0.4868913857677903</v>
       </c>
       <c r="E4" t="n">
         <v>141</v>
@@ -643,16 +643,16 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.6274999999999999</v>
+        <v>0.62</v>
       </c>
       <c r="C5" t="n">
-        <v>0.6274999999999999</v>
+        <v>0.62</v>
       </c>
       <c r="D5" t="n">
-        <v>0.6274999999999999</v>
+        <v>0.62</v>
       </c>
       <c r="E5" t="n">
-        <v>0.6274999999999999</v>
+        <v>0.62</v>
       </c>
     </row>
     <row r="6">
@@ -662,13 +662,13 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.6323268260049869</v>
+        <v>0.6093203093203093</v>
       </c>
       <c r="C6" t="n">
-        <v>0.5599819974875614</v>
+        <v>0.5463421268682552</v>
       </c>
       <c r="D6" t="n">
-        <v>0.5875023214548293</v>
+        <v>0.5712326466842771</v>
       </c>
       <c r="E6" t="n">
         <v>400</v>
@@ -681,13 +681,13 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.6177623380769932</v>
+        <v>0.6138534798534798</v>
       </c>
       <c r="C7" t="n">
-        <v>0.6274999999999999</v>
+        <v>0.62</v>
       </c>
       <c r="D7" t="n">
-        <v>0.618548815304829</v>
+        <v>0.6147931884919874</v>
       </c>
       <c r="E7" t="n">
         <v>400</v>
@@ -731,13 +731,13 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="C2" t="n">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="D2" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
     </row>
     <row r="3">
@@ -747,13 +747,13 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C3" t="n">
-        <v>182</v>
+        <v>174</v>
       </c>
       <c r="D3" t="n">
-        <v>54</v>
+        <v>61</v>
       </c>
     </row>
     <row r="4">
@@ -766,10 +766,10 @@
         <v>1</v>
       </c>
       <c r="C4" t="n">
-        <v>81</v>
+        <v>75</v>
       </c>
       <c r="D4" t="n">
-        <v>59</v>
+        <v>65</v>
       </c>
     </row>
   </sheetData>
@@ -783,7 +783,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B23"/>
+  <dimension ref="A1:B30"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -805,7 +805,7 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.3170965905362097</v>
+        <v>0.1869239031000937</v>
       </c>
     </row>
     <row r="3">
@@ -815,87 +815,87 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.3160122468179222</v>
+        <v>0.1737137219611846</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>feature_15</t>
+          <t>feature_27</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.07219749999595661</v>
+        <v>0.07315219424062275</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>feature_8</t>
+          <t>feature_6</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.07024353198956941</v>
+        <v>0.07094750940909597</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>feature_18</t>
+          <t>feature_15</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.03983575019248117</v>
+        <v>0.05678146419664117</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>feature_6</t>
+          <t>feature_8</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.03932480462263651</v>
+        <v>0.05223649195098416</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>feature_4</t>
+          <t>feature_16</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.03253270807821011</v>
+        <v>0.04553987533099606</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>feature_3</t>
+          <t>feature_12</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.01521527131758904</v>
+        <v>0.04524306644836552</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>feature_1</t>
+          <t>feature_11</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>0.01463612025551201</v>
+        <v>0.04343695126619058</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>feature_16</t>
+          <t>feature_1</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>0.0143509223815728</v>
+        <v>0.03211739099300394</v>
       </c>
     </row>
     <row r="12">
@@ -905,116 +905,186 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>0.01399815676227982</v>
+        <v>0.0295945083758975</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>feature_11</t>
+          <t>feature_18</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>0.01157059256567048</v>
+        <v>0.02864197479077822</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>feature_20</t>
+          <t>feature_3</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>0.0106389974866572</v>
+        <v>0.02504384197386074</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>feature_5</t>
+          <t>feature_4</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>0.01030405448487505</v>
+        <v>0.02144935263978315</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>feature_19</t>
+          <t>feature_5</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>0.01000581921925752</v>
+        <v>0.02093042650613483</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>feature_21</t>
+          <t>feature_19</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>0.007169270046027392</v>
+        <v>0.0206962991988572</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>feature_12</t>
+          <t>feature_22</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>0.004867663176748214</v>
+        <v>0.01856790747020347</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>feature_14</t>
+          <t>feature_21</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>7.082474880217134e-11</v>
+        <v>0.01667085214194831</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>feature_10</t>
+          <t>feature_26</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>0</v>
+        <v>0.01257494032444516</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>feature_9</t>
+          <t>feature_20</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>0</v>
+        <v>0.01028410911180228</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>feature_7</t>
+          <t>feature_23</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>0</v>
+        <v>0.008194898596463808</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
+          <t>feature_14</t>
+        </is>
+      </c>
+      <c r="B23" t="n">
+        <v>0.005525604731059531</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>feature_24</t>
+        </is>
+      </c>
+      <c r="B24" t="n">
+        <v>0.001732715241587196</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>feature_25</t>
+        </is>
+      </c>
+      <c r="B25" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
           <t>feature_0</t>
         </is>
       </c>
-      <c r="B23" t="n">
+      <c r="B26" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>feature_10</t>
+        </is>
+      </c>
+      <c r="B27" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>feature_9</t>
+        </is>
+      </c>
+      <c r="B28" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>feature_7</t>
+        </is>
+      </c>
+      <c r="B29" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>feature_28</t>
+        </is>
+      </c>
+      <c r="B30" t="n">
         <v>0</v>
       </c>
     </row>
